--- a/data_u1/data_doses_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_doses_2025-08-15_LSR3_H.xlsx
@@ -833,7 +833,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, monotherapy)  - part a</t>
+          <t>NCT03669640 (2018)  - part a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, monotherapy)  - part a</t>
+          <t>NCT03669640 (2018)  - part a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">

--- a/data_u1/data_doses_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/data_doses_2025-08-15_LSR3_H.xlsx
@@ -890,7 +890,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - part b</t>
+          <t>NCT03669640 (2018):addon - part b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - part b</t>
+          <t>NCT03669640 (2018):addon - part b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - part b</t>
+          <t>NCT03669640 (2018):addon - part b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,7 +1118,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - part b</t>
+          <t>NCT03669640 (2018):addon - part b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - part b</t>
+          <t>NCT03669640 (2018):addon - part b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NCT03669640 (2018, addon) - part b</t>
+          <t>NCT03669640 (2018):addon - part b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
